--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for ProcedureNotDoneReason, generated from enum_models.py.</t>
+    <t>Allowed coded values for ProcedureNotDoneReason</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>Not Required</t>
+  </si>
+  <si>
+    <t>low-aspect-score</t>
+  </si>
+  <si>
+    <t>Low ASPECTS Score</t>
+  </si>
+  <si>
+    <t>transfer-ivt</t>
+  </si>
+  <si>
+    <t>Transferred elsewhere to perform IVT</t>
   </si>
   <si>
     <t/>
@@ -514,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -702,15 +714,31 @@
         <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -737,34 +765,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -239,6 +239,30 @@
   </si>
   <si>
     <t>Transferred elsewhere to perform IVT</t>
+  </si>
+  <si>
+    <t>not-reported</t>
+  </si>
+  <si>
+    <t>Reason for not treating not reported</t>
+  </si>
+  <si>
+    <t>lesion-developed</t>
+  </si>
+  <si>
+    <t>Lesion Developed</t>
+  </si>
+  <si>
+    <t>previous-bleeding</t>
+  </si>
+  <si>
+    <t>Previous Bleeding</t>
+  </si>
+  <si>
+    <t>anticoagulant-use</t>
+  </si>
+  <si>
+    <t>Anticoagulant Use</t>
   </si>
   <si>
     <t/>
@@ -526,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -730,15 +754,47 @@
         <v>75</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -765,34 +821,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>Prognosis bad (finding)</t>
+  </si>
+  <si>
+    <t>385432009</t>
+  </si>
+  <si>
+    <t>Not applicable (qualifier value)</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -804,7 +810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -837,18 +843,26 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>90</v>
+      <c r="B6" t="s" s="2">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/procedure-not-done-reason-vs</t>
+    <t>http://qualityregistry.org/ValueSet/procedure-not-done-reason-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -271,7 +271,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/stroke-proc-not-done-reason-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/stroke-proc-not-done-reason-cs</t>
   </si>
   <si>
     <t>385660001</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-procedure-not-done-reason-vs.xlsx
+++ b/ValueSet-procedure-not-done-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
